--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -35,13 +35,10 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
-    <x:t>AKSGY</x:t>
-  </x:si>
-  <x:si>
     <x:t>ALKLC</x:t>
   </x:si>
   <x:si>
-    <x:t>AVGYO</x:t>
+    <x:t>AVPGY</x:t>
   </x:si>
   <x:si>
     <x:t>AYGAZ</x:t>
@@ -53,108 +50,78 @@
     <x:t>DEVA</x:t>
   </x:si>
   <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HURGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANHYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
     <x:t>DOHOL</x:t>
   </x:si>
   <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HURGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
   </x:si>
   <x:si>
     <x:t>ISDMR</x:t>
   </x:si>
   <x:si>
-    <x:t>KARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
+    <x:t>KCHOL</x:t>
   </x:si>
   <x:si>
     <x:t>METRO</x:t>
   </x:si>
   <x:si>
-    <x:t>PETKM</x:t>
+    <x:t>NETAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RALYH</x:t>
   </x:si>
   <x:si>
     <x:t>SKYMD</x:t>
   </x:si>
   <x:si>
-    <x:t>VAKBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALBRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVPGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYDEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENJSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCHOL</x:t>
-  </x:si>
-  <x:si>
     <x:t>SOKM</x:t>
   </x:si>
   <x:si>
@@ -167,19 +134,7 @@
     <x:t>TNZTP</x:t>
   </x:si>
   <x:si>
-    <x:t>TRALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRENJ</x:t>
-  </x:si>
-  <x:si>
     <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRMET</x:t>
   </x:si>
   <x:si>
     <x:t>TUPRS</x:t>
@@ -533,7 +488,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C26"/>
+  <x:dimension ref="A1:C15"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -698,127 +653,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:3">
-      <x:c r="A16" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B16" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C16" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:3">
-      <x:c r="A17" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B17" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C17" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:3">
-      <x:c r="A18" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B18" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C18" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:3">
-      <x:c r="A19" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B19" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C19" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:3">
-      <x:c r="A20" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B20" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C20" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:3">
-      <x:c r="A21" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B21" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C21" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:3">
-      <x:c r="A22" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B22" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C22" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:3">
-      <x:c r="A23" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B23" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C23" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:3">
-      <x:c r="A24" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C24" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:3">
-      <x:c r="A25" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B25" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C25" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:3">
-      <x:c r="A26" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B26" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C26" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -836,7 +670,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C27"/>
+  <x:dimension ref="A1:C23"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -852,7 +686,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -863,7 +697,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -874,7 +708,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -885,7 +719,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -896,7 +730,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -907,7 +741,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -918,7 +752,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -929,7 +763,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -940,7 +774,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -951,7 +785,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -962,7 +796,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -973,7 +807,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -984,7 +818,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -995,7 +829,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -1006,7 +840,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -1017,7 +851,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -1028,7 +862,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -1039,7 +873,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -1050,7 +884,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -1061,7 +895,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -1072,7 +906,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -1083,56 +917,12 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:3">
-      <x:c r="A24" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C24" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:3">
-      <x:c r="A25" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="B25" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C25" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:3">
-      <x:c r="A26" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="B26" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C26" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:3">
-      <x:c r="A27" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="B27" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C27" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -35,100 +35,49 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
+    <x:t>AVPGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EFOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
     <x:t>ALKLC</x:t>
   </x:si>
   <x:si>
-    <x:t>AVPGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HURGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
     <x:t>ANHYT</x:t>
   </x:si>
   <x:si>
-    <x:t>ARSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETAS</x:t>
+    <x:t>DSTKF</x:t>
   </x:si>
   <x:si>
     <x:t>OZATD</x:t>
   </x:si>
   <x:si>
-    <x:t>RALYH</x:t>
-  </x:si>
-  <x:si>
     <x:t>SKYMD</x:t>
   </x:si>
   <x:si>
-    <x:t>SOKM</x:t>
-  </x:si>
-  <x:si>
     <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
   </x:si>
   <x:si>
     <x:t>TNZTP</x:t>
@@ -488,7 +437,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C15"/>
+  <x:dimension ref="A1:C11"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -609,50 +558,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:3">
-      <x:c r="A12" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:3">
-      <x:c r="A13" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:3">
-      <x:c r="A14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C14" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:3">
-      <x:c r="A15" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B15" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C15" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -670,7 +575,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C23"/>
+  <x:dimension ref="A1:C10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -686,7 +591,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -697,7 +602,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -708,7 +613,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -719,7 +624,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -730,7 +635,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -741,7 +646,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -752,7 +657,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -763,7 +668,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -774,155 +679,12 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:3">
-      <x:c r="A11" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:3">
-      <x:c r="A12" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:3">
-      <x:c r="A13" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:3">
-      <x:c r="A14" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C14" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:3">
-      <x:c r="A15" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="B15" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C15" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:3">
-      <x:c r="A16" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="B16" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C16" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:3">
-      <x:c r="A17" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="B17" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C17" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:3">
-      <x:c r="A18" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="B18" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C18" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:3">
-      <x:c r="A19" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B19" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C19" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:3">
-      <x:c r="A20" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B20" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C20" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:3">
-      <x:c r="A21" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B21" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C21" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:3">
-      <x:c r="A22" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="B22" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C22" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:3">
-      <x:c r="A23" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="B23" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C23" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,7 +26,7 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
-    <x:t>AHGAZ</x:t>
+    <x:t>BMSTL</x:t>
   </x:si>
   <x:si>
     <x:t>Gün</x:t>
@@ -35,58 +35,16 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
-    <x:t>AVPGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSTL</x:t>
-  </x:si>
-  <x:si>
     <x:t>CELHA</x:t>
   </x:si>
   <x:si>
     <x:t>EFOR</x:t>
   </x:si>
   <x:si>
-    <x:t>ENERY</x:t>
+    <x:t>TKFEN</x:t>
   </x:si>
   <x:si>
     <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANHYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUPRS</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -437,7 +395,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C11"/>
+  <x:dimension ref="A1:C5"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -492,72 +450,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:3">
-      <x:c r="A6" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:3">
-      <x:c r="A7" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:3">
-      <x:c r="A8" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:3">
-      <x:c r="A9" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:3">
-      <x:c r="A10" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:3">
-      <x:c r="A11" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -575,7 +467,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C10"/>
+  <x:dimension ref="A1:C2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -591,100 +483,12 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:3">
-      <x:c r="A3" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:3">
-      <x:c r="A4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:3">
-      <x:c r="A5" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:3">
-      <x:c r="A6" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:3">
-      <x:c r="A7" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:3">
-      <x:c r="A8" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:3">
-      <x:c r="A9" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:3">
-      <x:c r="A10" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,25 +26,49 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANHYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
     <x:t>BMSTL</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EFOR</x:t>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISDMR</x:t>
   </x:si>
   <x:si>
     <x:t>TKFEN</x:t>
   </x:si>
   <x:si>
-    <x:t>EUKYO</x:t>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -395,7 +419,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C5"/>
+  <x:dimension ref="A1:C12"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -450,6 +474,83 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:3">
+      <x:c r="A6" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:3">
+      <x:c r="A7" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:3">
+      <x:c r="A8" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:3">
+      <x:c r="A9" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:3">
+      <x:c r="A10" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:3">
+      <x:c r="A11" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:3">
+      <x:c r="A12" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -467,7 +568,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C2"/>
+  <x:dimension ref="A1:C3"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -483,12 +584,23 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:3">
+      <x:c r="A3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,7 +26,7 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
-    <x:t>AGHOL</x:t>
+    <x:t>AHGAZ</x:t>
   </x:si>
   <x:si>
     <x:t>Gün</x:t>
@@ -35,28 +35,19 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANHYT</x:t>
+    <x:t>BAHKM</x:t>
   </x:si>
   <x:si>
     <x:t>BIMAS</x:t>
   </x:si>
   <x:si>
-    <x:t>BMSTL</x:t>
+    <x:t>EFOR</x:t>
   </x:si>
   <x:si>
     <x:t>ENERY</x:t>
   </x:si>
   <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
+    <x:t>INVES</x:t>
   </x:si>
   <x:si>
     <x:t>ISDMR</x:t>
@@ -419,7 +410,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C12"/>
+  <x:dimension ref="A1:C9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -518,39 +509,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:3">
-      <x:c r="A10" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:3">
-      <x:c r="A11" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:3">
-      <x:c r="A12" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -584,7 +542,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -595,7 +553,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -41,25 +41,22 @@
     <x:t>BIMAS</x:t>
   </x:si>
   <x:si>
-    <x:t>EFOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
     <x:t>ISDMR</x:t>
   </x:si>
   <x:si>
+    <x:t>KCHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
     <x:t>TKFEN</x:t>
   </x:si>
   <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
     <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKM</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -526,7 +523,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C3"/>
+  <x:dimension ref="A1:C2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -548,17 +545,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:3">
-      <x:c r="A3" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -35,28 +35,37 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
     <x:t>BAHKM</x:t>
   </x:si>
   <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
+    <x:t>DEVA</x:t>
   </x:si>
   <x:si>
     <x:t>KCHOL</x:t>
   </x:si>
   <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUPRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKM</x:t>
+    <x:t>KRDMD</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -407,7 +416,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C9"/>
+  <x:dimension ref="A1:C8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -495,17 +504,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:3">
-      <x:c r="A9" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -523,7 +521,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C2"/>
+  <x:dimension ref="A1:C6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -539,12 +537,56 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:3">
+      <x:c r="A3" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B2" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="s">
+      <x:c r="B3" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:3">
+      <x:c r="A4" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:3">
+      <x:c r="A5" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:3">
+      <x:c r="A6" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,46 +26,13 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
-    <x:t>AHGAZ</x:t>
+    <x:t>XU100</x:t>
   </x:si>
   <x:si>
     <x:t>Gün</x:t>
   </x:si>
   <x:si>
     <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -416,7 +383,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C8"/>
+  <x:dimension ref="A1:C1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -428,83 +395,6 @@
       </x:c>
       <x:c r="C1" s="0" t="s">
         <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:3">
-      <x:c r="A2" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B2" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:3">
-      <x:c r="A3" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:3">
-      <x:c r="A4" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:3">
-      <x:c r="A5" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:3">
-      <x:c r="A6" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:3">
-      <x:c r="A7" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:3">
-      <x:c r="A8" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -521,7 +411,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C6"/>
+  <x:dimension ref="A1:C2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -537,56 +427,12 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:3">
-      <x:c r="A3" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:3">
-      <x:c r="A4" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:3">
-      <x:c r="A5" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:3">
-      <x:c r="A6" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,13 +26,49 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
-    <x:t>XU100</x:t>
+    <x:t>AHGAZ</x:t>
   </x:si>
   <x:si>
     <x:t>Gün</x:t>
   </x:si>
   <x:si>
     <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRMET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -383,7 +419,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C1"/>
+  <x:dimension ref="A1:C6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -395,6 +431,61 @@
       </x:c>
       <x:c r="C1" s="0" t="s">
         <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:3">
+      <x:c r="A2" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:3">
+      <x:c r="A3" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:3">
+      <x:c r="A4" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:3">
+      <x:c r="A5" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:3">
+      <x:c r="A6" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -411,7 +502,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C2"/>
+  <x:dimension ref="A1:C9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -427,12 +518,89 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:3">
+      <x:c r="A3" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:3">
+      <x:c r="A4" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:3">
+      <x:c r="A5" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:3">
+      <x:c r="A6" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:3">
+      <x:c r="A7" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:3">
+      <x:c r="A8" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:3">
+      <x:c r="A9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,49 +26,55 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRMET</x:t>
+  </x:si>
+  <x:si>
     <x:t>AHGAZ</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
     <x:t>CELHA</x:t>
   </x:si>
   <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
     <x:t>ISDMR</x:t>
   </x:si>
   <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
     <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRMET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUPRS</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -419,7 +425,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C6"/>
+  <x:dimension ref="A1:C7"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -485,6 +491,17 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:3">
+      <x:c r="A7" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -502,7 +519,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C9"/>
+  <x:dimension ref="A1:C10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -518,7 +535,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -529,7 +546,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -540,7 +557,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -551,7 +568,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -562,7 +579,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -573,7 +590,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -584,7 +601,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -595,12 +612,23 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:3">
+      <x:c r="A10" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,52 +26,43 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYMD</x:t>
+  </x:si>
+  <x:si>
     <x:t>BAHKM</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRMET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
+    <x:t>BIMAS</x:t>
   </x:si>
   <x:si>
     <x:t>CELHA</x:t>
   </x:si>
   <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
+    <x:t>FLAP</x:t>
   </x:si>
   <x:si>
     <x:t>KRDMD</x:t>
   </x:si>
   <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
     <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYSAS</x:t>
   </x:si>
   <x:si>
     <x:t>TKFEN</x:t>
@@ -425,7 +416,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C7"/>
+  <x:dimension ref="A1:C5"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -480,28 +471,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:3">
-      <x:c r="A6" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:3">
-      <x:c r="A7" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -519,7 +488,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C10"/>
+  <x:dimension ref="A1:C9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -535,7 +504,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -546,7 +515,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -557,7 +526,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -568,7 +537,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -579,7 +548,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -590,7 +559,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -601,7 +570,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -612,23 +581,12 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:3">
-      <x:c r="A10" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -35,37 +35,25 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
     <x:t>HRKET</x:t>
   </x:si>
   <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
     <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -488,7 +476,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C9"/>
+  <x:dimension ref="A1:C5"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -543,50 +531,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:3">
-      <x:c r="A6" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:3">
-      <x:c r="A7" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:3">
-      <x:c r="A8" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:3">
-      <x:c r="A9" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,34 +26,31 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
     <x:t>ETILR</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYMD</x:t>
   </x:si>
   <x:si>
     <x:t>GMTAS</x:t>
   </x:si>
   <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
     <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -404,7 +401,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C5"/>
+  <x:dimension ref="A1:C6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -459,6 +456,17 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:3">
+      <x:c r="A6" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -476,7 +484,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C5"/>
+  <x:dimension ref="A1:C3"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -492,7 +500,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -503,34 +511,12 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:3">
-      <x:c r="A4" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:3">
-      <x:c r="A5" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,31 +26,40 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYMD</x:t>
+  </x:si>
+  <x:si>
     <x:t>AHGAZ</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
   </x:si>
   <x:si>
     <x:t>HUNER</x:t>
   </x:si>
   <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
+    <x:t>TKFEN</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -401,7 +410,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C6"/>
+  <x:dimension ref="A1:C5"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -456,17 +465,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:3">
-      <x:c r="A6" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -484,7 +482,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C3"/>
+  <x:dimension ref="A1:C7"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -500,7 +498,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -511,12 +509,56 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:3">
+      <x:c r="A4" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
+      <x:c r="B4" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:3">
+      <x:c r="A5" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:3">
+      <x:c r="A6" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:3">
+      <x:c r="A7" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,40 +26,37 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
     <x:t>ENERY</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
     <x:t>GMTAS</x:t>
   </x:si>
   <x:si>
     <x:t>HRKET</x:t>
   </x:si>
   <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
+    <x:t>KRPLS</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -410,7 +407,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C5"/>
+  <x:dimension ref="A1:C3"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -443,28 +440,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:3">
-      <x:c r="A4" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:3">
-      <x:c r="A5" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -482,7 +457,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C7"/>
+  <x:dimension ref="A1:C8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -498,7 +473,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -509,7 +484,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -520,7 +495,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -531,7 +506,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -542,7 +517,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -553,12 +528,23 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:3">
+      <x:c r="A8" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,37 +26,37 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
     <x:t>ETILR</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
     <x:t>HRKET</x:t>
   </x:si>
   <x:si>
-    <x:t>KRPLS</x:t>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -407,7 +407,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C3"/>
+  <x:dimension ref="A1:C1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -419,28 +419,6 @@
       </x:c>
       <x:c r="C1" s="0" t="s">
         <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:3">
-      <x:c r="A2" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B2" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:3">
-      <x:c r="A3" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -457,7 +435,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C8"/>
+  <x:dimension ref="A1:C10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -473,7 +451,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -484,7 +462,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -495,7 +473,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -506,7 +484,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -517,7 +495,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -528,7 +506,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -539,12 +517,34 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:3">
+      <x:c r="A9" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:3">
+      <x:c r="A10" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
+      <x:c r="B10" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,16 +26,22 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
     <x:t>AHGAZ</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRSAN</x:t>
   </x:si>
   <x:si>
     <x:t>CELHA</x:t>
@@ -44,13 +50,10 @@
     <x:t>ENERY</x:t>
   </x:si>
   <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
     <x:t>HRKET</x:t>
   </x:si>
   <x:si>
-    <x:t>ISDMR</x:t>
+    <x:t>INDES</x:t>
   </x:si>
   <x:si>
     <x:t>RYGYO</x:t>
@@ -407,7 +410,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C1"/>
+  <x:dimension ref="A1:C2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -419,6 +422,17 @@
       </x:c>
       <x:c r="C1" s="0" t="s">
         <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:3">
+      <x:c r="A2" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -451,7 +465,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -462,7 +476,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -473,7 +487,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -484,7 +498,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -495,7 +509,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -506,7 +520,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -517,7 +531,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -528,7 +542,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -539,7 +553,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -35,15 +35,21 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
     <x:t>AHGAZ</x:t>
   </x:si>
   <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALBRK</x:t>
+  </x:si>
+  <x:si>
     <x:t>AVGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>BRSAN</x:t>
-  </x:si>
-  <x:si>
     <x:t>CELHA</x:t>
   </x:si>
   <x:si>
@@ -51,12 +57,6 @@
   </x:si>
   <x:si>
     <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
   </x:si>
   <x:si>
     <x:t>TKFEN</x:t>
@@ -410,7 +410,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C2"/>
+  <x:dimension ref="A1:C3"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -432,6 +432,17 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:3">
+      <x:c r="A3" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -449,7 +460,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C10"/>
+  <x:dimension ref="A1:C9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -465,7 +476,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -476,7 +487,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -487,7 +498,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -498,7 +509,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -509,7 +520,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -520,7 +531,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -531,7 +542,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -542,23 +553,12 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:3">
-      <x:c r="A10" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -35,31 +35,25 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALBRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENJSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
     <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALBRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -410,7 +404,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C3"/>
+  <x:dimension ref="A1:C2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -432,17 +426,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:3">
-      <x:c r="A3" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -460,7 +443,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C9"/>
+  <x:dimension ref="A1:C8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -476,7 +459,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -487,7 +470,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -498,7 +481,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -509,7 +492,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -520,7 +503,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -531,7 +514,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -542,23 +525,12 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:3">
-      <x:c r="A9" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,34 +26,58 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
     <x:t>DURDO</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
+    <x:t>RYGYO</x:t>
   </x:si>
   <x:si>
     <x:t>AHGAZ</x:t>
   </x:si>
   <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
     <x:t>ALBRK</x:t>
   </x:si>
   <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
     <x:t>ENERY</x:t>
   </x:si>
   <x:si>
     <x:t>ENJSA</x:t>
   </x:si>
   <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
     <x:t>HRKET</x:t>
   </x:si>
   <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
     <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKBN</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -404,7 +428,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C2"/>
+  <x:dimension ref="A1:C4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -426,6 +450,28 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:3">
+      <x:c r="A3" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:3">
+      <x:c r="A4" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -443,7 +489,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C8"/>
+  <x:dimension ref="A1:C14"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -459,7 +505,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -470,7 +516,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -481,7 +527,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -492,7 +538,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -503,7 +549,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -514,7 +560,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -525,12 +571,78 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:3">
+      <x:c r="A9" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:3">
+      <x:c r="A10" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:3">
+      <x:c r="A11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:3">
+      <x:c r="A12" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:3">
+      <x:c r="A13" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:3">
+      <x:c r="A14" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -38,43 +38,25 @@
     <x:t>DURDO</x:t>
   </x:si>
   <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
     <x:t>AHGAZ</x:t>
   </x:si>
   <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
     <x:t>ALBRK</x:t>
   </x:si>
   <x:si>
     <x:t>ENERY</x:t>
   </x:si>
   <x:si>
-    <x:t>ENJSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
+    <x:t>GLYHO</x:t>
   </x:si>
   <x:si>
     <x:t>HRKET</x:t>
   </x:si>
   <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
     <x:t>INDES</x:t>
   </x:si>
   <x:si>
-    <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
     <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
   </x:si>
   <x:si>
     <x:t>VAKBN</x:t>
@@ -428,7 +410,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C4"/>
+  <x:dimension ref="A1:C3"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -461,17 +443,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:3">
-      <x:c r="A4" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -489,7 +460,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C14"/>
+  <x:dimension ref="A1:C9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -505,7 +476,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -516,7 +487,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -527,7 +498,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -538,7 +509,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -549,7 +520,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -560,7 +531,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -571,7 +542,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -582,67 +553,12 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:3">
-      <x:c r="A10" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:3">
-      <x:c r="A11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:3">
-      <x:c r="A12" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:3">
-      <x:c r="A13" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:3">
-      <x:c r="A14" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C14" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,7 +26,7 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
-    <x:t>CELHA</x:t>
+    <x:t>RYGYO</x:t>
   </x:si>
   <x:si>
     <x:t>Gün</x:t>
@@ -38,16 +38,16 @@
     <x:t>DURDO</x:t>
   </x:si>
   <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALBRK</x:t>
-  </x:si>
-  <x:si>
     <x:t>ENERY</x:t>
   </x:si>
   <x:si>
+    <x:t>ENJSA</x:t>
+  </x:si>
+  <x:si>
     <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
   </x:si>
   <x:si>
     <x:t>HRKET</x:t>
@@ -410,7 +410,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C3"/>
+  <x:dimension ref="A1:C2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -432,17 +432,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:3">
-      <x:c r="A3" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -460,7 +449,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C9"/>
+  <x:dimension ref="A1:C10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -476,7 +465,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -487,7 +476,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -498,7 +487,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -509,7 +498,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -520,7 +509,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -531,7 +520,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -542,7 +531,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -553,12 +542,23 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:3">
+      <x:c r="A10" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
+      <x:c r="B10" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,22 +26,25 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
     <x:t>RYGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENJSA</x:t>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
   </x:si>
   <x:si>
     <x:t>GLYHO</x:t>
@@ -56,7 +59,7 @@
     <x:t>INDES</x:t>
   </x:si>
   <x:si>
-    <x:t>ORGE</x:t>
+    <x:t>SOKM</x:t>
   </x:si>
   <x:si>
     <x:t>VAKBN</x:t>
@@ -410,7 +413,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C2"/>
+  <x:dimension ref="A1:C4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -432,6 +435,28 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:3">
+      <x:c r="A3" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:3">
+      <x:c r="A4" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -449,7 +474,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C10"/>
+  <x:dimension ref="A1:C9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -465,7 +490,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -476,7 +501,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -487,7 +512,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -498,7 +523,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -509,7 +534,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -520,7 +545,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -531,7 +556,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -542,23 +567,12 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:3">
-      <x:c r="A10" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,7 +26,7 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
-    <x:t>CELHA</x:t>
+    <x:t>SOKM</x:t>
   </x:si>
   <x:si>
     <x:t>Gün</x:t>
@@ -35,19 +35,16 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
+    <x:t>AHGAZ</x:t>
   </x:si>
   <x:si>
     <x:t>ALARK</x:t>
   </x:si>
   <x:si>
-    <x:t>GLYHO</x:t>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENJSA</x:t>
   </x:si>
   <x:si>
     <x:t>GMTAS</x:t>
@@ -57,12 +54,6 @@
   </x:si>
   <x:si>
     <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKBN</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -413,7 +404,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C4"/>
+  <x:dimension ref="A1:C2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -435,28 +426,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:3">
-      <x:c r="A3" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:3">
-      <x:c r="A4" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -474,7 +443,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C9"/>
+  <x:dimension ref="A1:C8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -490,7 +459,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -501,7 +470,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -512,7 +481,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -523,7 +492,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -534,7 +503,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -545,7 +514,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -556,23 +525,12 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:3">
-      <x:c r="A9" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,7 +26,7 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
-    <x:t>SOKM</x:t>
+    <x:t>GLYHO</x:t>
   </x:si>
   <x:si>
     <x:t>Gün</x:t>
@@ -35,25 +35,10 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENJSA</x:t>
-  </x:si>
-  <x:si>
     <x:t>GMTAS</x:t>
   </x:si>
   <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
+    <x:t>RYSAS</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -443,7 +428,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C8"/>
+  <x:dimension ref="A1:C3"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -476,61 +461,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:3">
-      <x:c r="A4" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:3">
-      <x:c r="A5" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:3">
-      <x:c r="A6" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:3">
-      <x:c r="A7" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:3">
-      <x:c r="A8" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,7 +26,7 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
-    <x:t>GLYHO</x:t>
+    <x:t>SOKM</x:t>
   </x:si>
   <x:si>
     <x:t>Gün</x:t>
@@ -36,9 +36,6 @@
   </x:si>
   <x:si>
     <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYSAS</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -428,7 +425,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C3"/>
+  <x:dimension ref="A1:C2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -450,17 +447,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:3">
-      <x:c r="A3" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,13 +26,34 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENJSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
     <x:t>SOKM</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLYHO</x:t>
   </x:si>
   <x:si>
     <x:t>GMTAS</x:t>
@@ -386,7 +407,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C2"/>
+  <x:dimension ref="A1:C5"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -408,6 +429,39 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:3">
+      <x:c r="A3" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:3">
+      <x:c r="A4" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:3">
+      <x:c r="A5" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -425,7 +479,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C2"/>
+  <x:dimension ref="A1:C6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -441,12 +495,56 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:3">
+      <x:c r="A3" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:3">
+      <x:c r="A4" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:3">
+      <x:c r="A5" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:3">
+      <x:c r="A6" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,7 +26,7 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
-    <x:t>DURDO</x:t>
+    <x:t>ENJSA</x:t>
   </x:si>
   <x:si>
     <x:t>Gün</x:t>
@@ -35,28 +35,10 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
-    <x:t>ENJSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
     <x:t>ETILR</x:t>
   </x:si>
   <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
+    <x:t>RYGYO</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -407,7 +389,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C5"/>
+  <x:dimension ref="A1:C2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -429,39 +411,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:3">
-      <x:c r="A3" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:3">
-      <x:c r="A4" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:3">
-      <x:c r="A5" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -479,7 +428,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C6"/>
+  <x:dimension ref="A1:C3"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -495,7 +444,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -506,45 +455,12 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:3">
-      <x:c r="A4" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:3">
-      <x:c r="A5" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:3">
-      <x:c r="A6" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,19 +26,13 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
-    <x:t>ENJSA</x:t>
+    <x:t>RYGYO</x:t>
   </x:si>
   <x:si>
     <x:t>Gün</x:t>
   </x:si>
   <x:si>
     <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -389,7 +383,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C2"/>
+  <x:dimension ref="A1:C1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -401,17 +395,6 @@
       </x:c>
       <x:c r="C1" s="0" t="s">
         <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:3">
-      <x:c r="A2" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B2" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -428,7 +411,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C3"/>
+  <x:dimension ref="A1:C2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -444,23 +427,12 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:3">
-      <x:c r="A3" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,13 +26,25 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
     <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -383,7 +395,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C1"/>
+  <x:dimension ref="A1:C3"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -395,6 +407,28 @@
       </x:c>
       <x:c r="C1" s="0" t="s">
         <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:3">
+      <x:c r="A2" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:3">
+      <x:c r="A3" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -411,7 +445,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C2"/>
+  <x:dimension ref="A1:C4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -427,12 +461,34 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:3">
+      <x:c r="A3" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:3">
+      <x:c r="A4" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,22 +26,13 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
-    <x:t>DOCO</x:t>
+    <x:t>GMTAS</x:t>
   </x:si>
   <x:si>
     <x:t>Gün</x:t>
   </x:si>
   <x:si>
     <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
   </x:si>
   <x:si>
     <x:t>RYGYO</x:t>
@@ -445,7 +436,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C4"/>
+  <x:dimension ref="A1:C1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -457,39 +448,6 @@
       </x:c>
       <x:c r="C1" s="0" t="s">
         <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:3">
-      <x:c r="A2" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B2" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:3">
-      <x:c r="A3" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:3">
-      <x:c r="A4" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
+++ b/app/borsa/gosterge-taramalari/data/yükselis-hacim.xlsx
@@ -26,16 +26,19 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
     <x:t>GMTAS</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
+    <x:t>AHGAZ</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -436,7 +439,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C1"/>
+  <x:dimension ref="A1:C2"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -448,6 +451,17 @@
       </x:c>
       <x:c r="C1" s="0" t="s">
         <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:3">
+      <x:c r="A2" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
